--- a/Dallas_Mavericks_2025-26_stats.xlsx
+++ b/Dallas_Mavericks_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,6 +1245,66 @@
         <v>19</v>
       </c>
       <c r="R13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>28</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>28</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>13</v>
+      </c>
+      <c r="R14" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1259,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2072,6 +2132,66 @@
       </c>
       <c r="R13" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2085,7 +2205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2898,6 +3018,66 @@
       </c>
       <c r="R13" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2911,7 +3091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3724,6 +3904,66 @@
       </c>
       <c r="R13" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3769,7 +4009,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.08333333333333</v>
+        <v>15.15384615384615</v>
       </c>
     </row>
     <row r="4">
@@ -3789,7 +4029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>12.76923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -3799,27 +4039,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.91666666666667</v>
+        <v>12.23076923076923</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brandon Williams</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.5</v>
+        <v>11.69230769230769</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Brandon Williams</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.33333333333333</v>
+        <v>10.18181818181818</v>
       </c>
     </row>
     <row r="9">
@@ -3829,7 +4069,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.428571428571429</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="10">
@@ -3839,7 +4079,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.454545454545455</v>
+        <v>8.833333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -3849,7 +4089,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.333333333333333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -3869,7 +4109,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.75</v>
+        <v>4.333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -3899,7 +4139,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4</v>
+        <v>1.454545454545455</v>
       </c>
     </row>
     <row r="17">
@@ -3945,67 +4185,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.75</v>
+        <v>4.769230769230769</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Brandon Williams</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.333333333333333</v>
+        <v>3.090909090909091</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dereck Lively II</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>3.076923076923077</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brandon Williams</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9</v>
+        <v>2.615384615384615</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.833333333333333</v>
+        <v>2.384615384615385</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.416666666666667</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Dereck Lively II</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.333333333333333</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -4025,7 +4265,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.909090909090909</v>
+        <v>1.916666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -4041,21 +4281,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Caleb Martin</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Caleb Martin</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -4085,7 +4325,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="17">
@@ -4151,7 +4391,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.75</v>
+        <v>6.615384615384615</v>
       </c>
     </row>
     <row r="5">
@@ -4161,7 +4401,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.571428571428571</v>
+        <v>5.875</v>
       </c>
     </row>
     <row r="6">
@@ -4181,7 +4421,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.333333333333333</v>
+        <v>4.615384615384615</v>
       </c>
     </row>
     <row r="8">
@@ -4191,7 +4431,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3.888888888888889</v>
       </c>
     </row>
     <row r="9">
@@ -4201,27 +4441,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.25</v>
+        <v>3.538461538461538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>D'Angelo Russell</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.818181818181818</v>
+        <v>2.923076923076923</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D'Angelo Russell</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.666666666666667</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="12">
@@ -4231,7 +4471,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4</v>
+        <v>2.363636363636364</v>
       </c>
     </row>
     <row r="13">
@@ -4251,7 +4491,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4</v>
+        <v>1.636363636363636</v>
       </c>
     </row>
     <row r="15">
@@ -4317,7 +4557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.666666666666667</v>
+        <v>2.692307692307693</v>
       </c>
     </row>
     <row r="3">
@@ -4327,7 +4567,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -4337,7 +4577,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.333333333333333</v>
+        <v>1.230769230769231</v>
       </c>
     </row>
     <row r="5">
@@ -4347,7 +4587,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.166666666666667</v>
+        <v>1.076923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -4377,7 +4617,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="9">
@@ -4397,7 +4637,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="11">
@@ -4407,7 +4647,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="12">
@@ -4481,7 +4721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4763,6 +5003,27 @@
         <v>237</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>127</v>
+      </c>
+      <c r="D14" t="n">
+        <v>133</v>
+      </c>
+      <c r="E14" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
